--- a/web/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
+++ b/web/files/港岛-黄泥涌-Eight Kwai Fong Happy Valley.xlsx
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
+          <t>2021-12-06</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
+          <t>2021-12-06</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2020-11-23</t>
+          <t>2020-11-24</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -11735,7 +11735,7 @@
           <t>A | 411呎 (1房)
 $1494万
 $36,350/呎
-(20年-11月-12日)</t>
+(20年-11月-13日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -12010,7 +12010,7 @@
           <t>A | 410呎 (1房)
 $1387万
 $33,824/呎
-(21年-12月-05日)</t>
+(21年-12月-06日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -12018,7 +12018,7 @@
           <t>B | 401呎 (1房)
 $1378万
 $34,374/呎
-(21年-12月-05日)</t>
+(21年-12月-06日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -12065,7 +12065,7 @@
           <t>A | 410呎 (1房)
 $1454万
 $35,451/呎
-(20年-11月-12日)</t>
+(20年-11月-13日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -12120,7 +12120,7 @@
           <t>A | 410呎 (1房)
 $1432万
 $34,929/呎
-(20年-11月-11日)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -12215,7 +12215,7 @@
           <t>F | 426呎 (1房)
 $1394万
 $32,721/呎
-(21年-06月-17日)</t>
+(21年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
           <t>A | 410呎 (1房)
 $1390万
 $33,905/呎
-(20年-11月-25日)</t>
+(20年-11月-26日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -12270,7 +12270,7 @@
           <t>F | 426呎 (1房)
 $1376万
 $32,303/呎
-(20年-11月-18日)</t>
+(20年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
           <t>B | 401呎 (1房)
 $1375万
 $34,284/呎
-(21年-03月-02日)</t>
+(21年-03月-03日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -12325,7 +12325,7 @@
           <t>F | 426呎 (1房)
 $1358万
 $31,887/呎
-(20年-12月-20日)</t>
+(20年-12月-21日)</t>
         </is>
       </c>
     </row>
@@ -12340,7 +12340,7 @@
           <t>A | 410呎 (1房)
 $1268万
 $30,934/呎
-(20年-10月-25日)</t>
+(20年-10月-26日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -12348,7 +12348,7 @@
           <t>B | 401呎 (1房)
 $1273万
 $31,751/呎
-(20年-11月-15日)</t>
+(20年-11月-16日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -12380,7 +12380,7 @@
           <t>F | 426呎 (1房)
 $1341万
 $31,479/呎
-(21年-03月-29日)</t>
+(21年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
           <t>F | 428呎 (1房)
 $1324万
 $30,930/呎
-(21年-01月-12日)</t>
+(21年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12450,7 @@
           <t>A | 410呎 (1房)
 $1312万
 $32,010/呎
-(20年-11月-18日)</t>
+(20年-11月-19日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -12458,7 +12458,7 @@
           <t>B | 402呎 (1房)
 $1239万
 $30,813/呎
-(20年-11月-18日)</t>
+(20年-11月-19日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -12505,7 +12505,7 @@
           <t>A | 410呎 (1房)
 $1293万
 $31,537/呎
-(20年-11月-11日)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -12513,7 +12513,7 @@
           <t>B | 401呎 (1房)
 $1299万
 $32,392/呎
-(20年-11月-11日)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -12545,7 +12545,7 @@
           <t>F | 426呎 (1房)
 $1242万
 $29,164/呎
-(20年-11月-23日)</t>
+(20年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
           <t>A | 410呎 (1房)
 $1274万
 $31,071/呎
-(20年-11月-11日)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -12568,7 +12568,7 @@
           <t>B | 401呎 (1房)
 $1280万
 $31,925/呎
-(20年-11月-11日)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -12592,7 +12592,7 @@
           <t>E | 397呎 (1房)
 $1202万
 $30,282/呎
-(22年-04月-28日)</t>
+(22年-04月-29日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -12600,7 +12600,7 @@
           <t>F | 426呎 (1房)
 $1206万
 $28,310/呎
-(20年-12月-01日)</t>
+(20年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
           <t>A | 410呎 (1房)
 $1281万
 $31,249/呎
-(21年-03月-10日)</t>
+(21年-03月-11日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -12623,7 +12623,7 @@
           <t>B | 402呎 (1房)
 $1176万
 $29,246/呎
-(20年-11月-17日)</t>
+(20年-11月-18日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -12647,7 +12647,7 @@
           <t>E | 397呎 (1房)
 $1154万
 $29,076/呎
-(21年-01月-12日)</t>
+(21年-01月-13日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
